--- a/artfynd/A 2305-2025 artfynd.xlsx
+++ b/artfynd/A 2305-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90840594</v>
+        <v>90840613</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ca 360 m N om Västgårdsbodarna, Jmt</t>
+          <t>ca 460 m N om Västgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508131.9525968736</v>
+        <v>508308</v>
       </c>
       <c r="R2" t="n">
-        <v>7055833.016607924</v>
+        <v>7055927</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2019-09-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,11 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stående död gran</t>
-        </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -801,50 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90840617</v>
+        <v>90840631</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ca 500 m N om Västgårdsbodarna, Jmt</t>
+          <t>ca 430 m N om Västgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508083.0753291998</v>
+        <v>508258</v>
       </c>
       <c r="R3" t="n">
-        <v>7055971.156561208</v>
+        <v>7055879</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,19 +849,9 @@
           <t>2019-09-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,11 +862,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>granhögstubbe</t>
-        </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -927,50 +887,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90840613</v>
+        <v>90840639</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>ca 460 m N om Västgårdsbodarna, Jmt</t>
+          <t>ca 360 m N om Västgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508307.9990491308</v>
+        <v>508123</v>
       </c>
       <c r="R4" t="n">
-        <v>7055926.836119088</v>
+        <v>7055845</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1000,19 +955,9 @@
           <t>2019-09-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,374 +986,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>90840612</v>
-      </c>
-      <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>ca 460 m N om Västgårdsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>508307.9990491308</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7055926.836119088</v>
-      </c>
-      <c r="S5" t="n">
-        <v>25</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Hammerdal</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2019-09-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2019-09-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>90840631</v>
-      </c>
-      <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>ca 430 m N om Västgårdsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>508257.8191670665</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7055879.134692261</v>
-      </c>
-      <c r="S6" t="n">
-        <v>25</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Hammerdal</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2019-09-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2019-09-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>90840639</v>
-      </c>
-      <c r="B7" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>ca 360 m N om Västgårdsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>508123.0182322861</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7055844.997647565</v>
-      </c>
-      <c r="S7" t="n">
-        <v>25</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Hammerdal</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2019-09-23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2019-09-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>

--- a/artfynd/A 2305-2025 artfynd.xlsx
+++ b/artfynd/A 2305-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90840613</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90840631</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,8 +1005,18 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90840639</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>